--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/staggered_10_accounts_hold_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/staggered_10_accounts_hold_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -466,12 +466,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.02317099207360573</v>
+        <v>-0.0923689384437133</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2764140730022742</v>
+        <v>0.1634741114738042</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.01174066237389502</v>
+        <v>-0.6791455561411458</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.01613593064862247</v>
+        <v>-0.8781015079808628</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2563871568268329</v>
+        <v>0.156726784032253</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.1019729004485674</v>
+        <v>-0.6618943074608321</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>11.70259654253515</v>
+        <v>9.281451430020777</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2244922430652874</v>
+        <v>-0.2365842130492248</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2291381878514383</v>
+        <v>0.2551134223986407</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.105103007568314</v>
+        <v>-1.032236385027934</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.438671440757839</v>
+        <v>-1.365313079041546</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2725987623236571</v>
+        <v>0.2998401886010007</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8532570933947239</v>
+        <v>-0.8172781690292901</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>13.42345697702143</v>
+        <v>12.07367933549636</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.03278680615725793</v>
+        <v>0.1378581320763315</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2093812292525177</v>
+        <v>0.1908903916566802</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.1327398303711668</v>
+        <v>0.7216146910232032</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.1925243955660663</v>
+        <v>1.085297602244983</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2035969252125209</v>
+        <v>0.17151820802255</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.167577474646805</v>
+        <v>0.8392505430437933</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>13.28967101739187</v>
+        <v>13.33254895195299</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1000214538648589</v>
+        <v>0.0328610265186764</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2130956164129167</v>
+        <v>0.2348583536806201</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.5018541857396731</v>
+        <v>0.196594754601627</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.7456833380157046</v>
+        <v>0.286196006753044</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1606438234315374</v>
+        <v>0.1706289304762754</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.6496561750512686</v>
+        <v>0.2006805808972897</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>13.89399717921153</v>
+        <v>15.92971305136156</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.4016259637484649</v>
+        <v>0.485557599282048</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2470601369134694</v>
+        <v>0.2601101551247655</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.48210048890637</v>
+        <v>1.652387190891094</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.077636956223887</v>
+        <v>2.390339436872697</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1409817629173796</v>
+        <v>0.1559317639207288</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.973882782317577</v>
+        <v>3.254594280303618</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>15.67626706577493</v>
+        <v>14.79118466797412</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.06820056309739919</v>
+        <v>0.1951513902172779</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.337164120854873</v>
+        <v>0.3599931874205319</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4786932836215854</v>
+        <v>1.035554186051899</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.6761415882378323</v>
+        <v>1.537449358216771</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2210149106925575</v>
+        <v>0.1302644821812434</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5748822008366203</v>
+        <v>2.928973762887527</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>13.2882252574318</v>
+        <v>12.27628191667418</v>
       </c>
     </row>
   </sheetData>
